--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260828.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260828.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>133,185</t>
+          <t>133,635</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.88%</t>
+          <t>27.24%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>96,680</t>
+          <t>96,880</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.97%</t>
+          <t>8.07%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.88%</t>
+          <t>7.67%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>49,125</t>
+          <t>49,275</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.44%</t>
+          <t>5.89%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>117,145</t>
+          <t>117,245</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>5.30%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>57,540</t>
+          <t>57,740</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.61%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>63,155</t>
+          <t>63,255</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>17,713</t>
+          <t>17,813</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>43,555</t>
+          <t>43,655</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
@@ -853,56 +853,56 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>74,415</t>
+          <t>74,565</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>19,565</t>
+          <t>30,460</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>30,460</t>
+          <t>19,565</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>18,820</t>
+          <t>18,920</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>57,288</t>
+          <t>57,388</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1029,29 +1029,29 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>11,251</t>
+          <t>11,351</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>7,690</t>
+          <t>72,515,261</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,22 +1063,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9,236</t>
+          <t>7,690</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1095,122 +1095,122 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>20,538</t>
+          <t>20,688</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>122,385</t>
+          <t>9,336</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>17,745</t>
+          <t>122,585</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>57,488,699</t>
+          <t>17,845</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,867</t>
+          <t>15,471</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,371</t>
+          <t>18,967</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>720,169</t>
+          <t>346,257</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>-73,912</t>
+          <t>263,979</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
